--- a/artfynd/A 49945-2025 artfynd.xlsx
+++ b/artfynd/A 49945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104043985</v>
+        <v>82883728</v>
       </c>
       <c r="B2" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>2326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Nees</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Snärmossen, Vstm</t>
+          <t>Hallfallsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528678.7328085892</v>
+        <v>528818</v>
       </c>
       <c r="R2" t="n">
-        <v>6614806.27491644</v>
+        <v>6614690</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,57 +757,61 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Stråk med lövrik barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fuktig humus</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104043983</v>
+        <v>104043985</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528627.7169493344</v>
+        <v>528678</v>
       </c>
       <c r="R3" t="n">
-        <v>6614793.75945773</v>
+        <v>6614806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,21 +863,11 @@
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +879,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116137986</v>
+        <v>73370932</v>
       </c>
       <c r="B4" t="n">
-        <v>96696</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,38 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>4379</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Luckes källa, Vstm</t>
+          <t>Hallfallsmossen - Gälsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528852</v>
+        <v>528634</v>
       </c>
       <c r="R4" t="n">
-        <v>6614749</v>
+        <v>6614745</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2018-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +983,238 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104043983</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Snärmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528628</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6614794</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116137986</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Luckes källa, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>528852</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6614749</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Anders Carlberg</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Anders Carlberg, Camilla Pettersson, Herbert Kaufmann, Kari Storvestre</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49945-2025 artfynd.xlsx
+++ b/artfynd/A 49945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883728</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104043985</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73370932</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104043983</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,8 +1240,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116137986</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>